--- a/Inputs.xlsx
+++ b/Inputs.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12000"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12000" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Precios" sheetId="3" r:id="rId1"/>
@@ -28993,7 +28993,7 @@
         <v>46203</v>
       </c>
       <c r="C3" s="8">
-        <v>46417</v>
+        <v>46598</v>
       </c>
       <c r="D3" s="7">
         <v>5.3999999999999999E-2</v>
